--- a/tests/regression_artifacts/downloads/email_03152025_FASHIOMiOVA/current/138878183.xlsx
+++ b/tests/regression_artifacts/downloads/email_03152025_FASHIOMiOVA/current/138878183.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Invoice Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Invoice Data" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -917,19 +917,19 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Brassiéres</t>
+          <t>Corselettes</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>62121000</t>
+          <t>62123000</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr"/>
       <c r="H4" s="2" t="inlineStr"/>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>62121000</t>
+          <t>62123000</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -981,7 +981,7 @@
       <c r="AJ4" s="2" t="n"/>
       <c r="AK4" s="2" t="inlineStr">
         <is>
-          <t>62121000</t>
+          <t>62123000</t>
         </is>
       </c>
     </row>
@@ -993,7 +993,7 @@
       <c r="E5" s="4" t="n"/>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>62121000</t>
+          <t>62123000</t>
         </is>
       </c>
       <c r="G5" s="4" t="n"/>
@@ -1117,11 +1117,7 @@
       <c r="AH6" s="4" t="n"/>
       <c r="AI6" s="4" t="n"/>
       <c r="AJ6" s="4" t="n"/>
-      <c r="AK6" s="4" t="inlineStr">
-        <is>
-          <t>62123000</t>
-        </is>
-      </c>
+      <c r="AK6" s="4" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n"/>
@@ -1138,19 +1134,19 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Trousers and shorts</t>
+          <t>Other Of other textile materials</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>62046910</t>
+          <t>62046990</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr"/>
       <c r="H7" s="2" t="inlineStr"/>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>62046910</t>
+          <t>62046990</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1202,7 +1198,7 @@
       <c r="AJ7" s="2" t="n"/>
       <c r="AK7" s="2" t="inlineStr">
         <is>
-          <t>62046910</t>
+          <t>62046990</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1210,7 @@
       <c r="E8" s="4" t="n"/>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>62046910</t>
+          <t>62046990</t>
         </is>
       </c>
       <c r="G8" s="4" t="n"/>
@@ -1281,7 +1277,7 @@
       <c r="E9" s="4" t="n"/>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>62045900</t>
+          <t>62046990</t>
         </is>
       </c>
       <c r="G9" s="4" t="n"/>
@@ -1338,11 +1334,7 @@
       <c r="AH9" s="4" t="n"/>
       <c r="AI9" s="4" t="n"/>
       <c r="AJ9" s="4" t="n"/>
-      <c r="AK9" s="4" t="inlineStr">
-        <is>
-          <t>62045900</t>
-        </is>
-      </c>
+      <c r="AK9" s="4" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="6" t="n"/>
@@ -2099,7 +2091,7 @@
       <c r="I30" s="13" t="n"/>
       <c r="J30" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">  └ 62046910: 20% CET (74% of value)</t>
+          <t xml:space="preserve">  └ 62046990: 20% CET (74% of value)</t>
         </is>
       </c>
       <c r="K30" s="13" t="n"/>
@@ -2144,7 +2136,7 @@
       <c r="I31" s="13" t="n"/>
       <c r="J31" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">  └ 62121000: 20% CET (18% of value)</t>
+          <t xml:space="preserve">  └ 62123000: 20% CET (18% of value)</t>
         </is>
       </c>
       <c r="K31" s="13" t="n"/>
